--- a/anthola_fullstack/backend/exports/bookings-latest.xlsx
+++ b/anthola_fullstack/backend/exports/bookings-latest.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="22">
   <si>
     <t>Booking ID</t>
   </si>
@@ -49,25 +49,25 @@
     <t>Created at</t>
   </si>
   <si>
-    <t>BKG-1781810227615-667</t>
+    <t>BKG-1785835183317-407</t>
   </si>
   <si>
     <t>BUS</t>
   </si>
   <si>
-    <t>ayushi</t>
-  </si>
-  <si>
-    <t>ktm -&gt; mnr</t>
-  </si>
-  <si>
-    <t>123</t>
-  </si>
-  <si>
-    <t>2026-06-18</t>
-  </si>
-  <si>
-    <t>S01 | S02 | S05 | S06 | S09 | S10 | S13 | S14</t>
+    <t>kshitiz.thapa</t>
+  </si>
+  <si>
+    <t>Kathmandu -&gt; Pokhara</t>
+  </si>
+  <si>
+    <t>ktm-pok</t>
+  </si>
+  <si>
+    <t>2026-08-04</t>
+  </si>
+  <si>
+    <t>S01 | S02</t>
   </si>
   <si>
     <t>NPR</t>
@@ -76,130 +76,7 @@
     <t>PAYMENT_UPLOADED</t>
   </si>
   <si>
-    <t>2026-06-18T19:17:07.624Z</t>
-  </si>
-  <si>
-    <t>BKG-1781807108374-129</t>
-  </si>
-  <si>
-    <t>sss</t>
-  </si>
-  <si>
-    <t>Kathmandu -&gt; dharan</t>
-  </si>
-  <si>
-    <t>ktm-Mnr</t>
-  </si>
-  <si>
-    <t>S09 | S10 | S11 | S13 | S14 | S17 | S27</t>
-  </si>
-  <si>
-    <t>PAYMENT_REVIEW</t>
-  </si>
-  <si>
-    <t>RECEIVED</t>
-  </si>
-  <si>
-    <t>2026-06-18T18:25:08.380Z</t>
-  </si>
-  <si>
-    <t>BKG-1781807059470-452</t>
-  </si>
-  <si>
-    <t>S01 | S02 | S03 | S04 | S05 | S06 | S07 | S08</t>
-  </si>
-  <si>
-    <t>PENDING_PAYMENT</t>
-  </si>
-  <si>
-    <t>PENDING</t>
-  </si>
-  <si>
-    <t>2026-06-18T18:24:19.479Z</t>
-  </si>
-  <si>
-    <t>BKG-1781805246854-189</t>
-  </si>
-  <si>
-    <t>admin</t>
-  </si>
-  <si>
-    <t>Kathmandu -&gt; kanchanpur</t>
-  </si>
-  <si>
-    <t>2026-06-19</t>
-  </si>
-  <si>
-    <t>CONFIRMED</t>
-  </si>
-  <si>
-    <t>APPROVED</t>
-  </si>
-  <si>
-    <t>2026-06-18T17:54:06.865Z</t>
-  </si>
-  <si>
-    <t>BKG-1768675496397-571</t>
-  </si>
-  <si>
-    <t>rohan</t>
-  </si>
-  <si>
-    <t>2026-01-18</t>
-  </si>
-  <si>
-    <t>D1 | D2</t>
-  </si>
-  <si>
-    <t>SUCCESS</t>
-  </si>
-  <si>
-    <t>2026-01-17T18:44:56.400Z</t>
-  </si>
-  <si>
-    <t>BKG-1768675153863-535</t>
-  </si>
-  <si>
-    <t>ayush</t>
-  </si>
-  <si>
-    <t>B1 | B2 | C1 | C2</t>
-  </si>
-  <si>
-    <t>2026-01-17T18:39:13.866Z</t>
-  </si>
-  <si>
-    <t>BKG-1768675145354-704</t>
-  </si>
-  <si>
-    <t>A1 | A2</t>
-  </si>
-  <si>
-    <t>2026-01-17T18:39:05.357Z</t>
-  </si>
-  <si>
-    <t>BKG-1768675003597-421</t>
-  </si>
-  <si>
-    <t>Kathmandu -&gt; Chitwan</t>
-  </si>
-  <si>
-    <t>ktm-chi</t>
-  </si>
-  <si>
-    <t>2026-01-17T18:36:43.601Z</t>
-  </si>
-  <si>
-    <t>BKG-1768671335801-636</t>
-  </si>
-  <si>
-    <t>2026-01-17</t>
-  </si>
-  <si>
-    <t>A1 | B1</t>
-  </si>
-  <si>
-    <t>2026-01-17T17:35:35.804Z</t>
+    <t>2026-08-04T09:19:43.326Z</t>
   </si>
 </sst>
 </file>
@@ -586,7 +463,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:L2"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="22" style="1" customWidth="1"/>
@@ -663,7 +540,7 @@
         <v>18</v>
       </c>
       <c r="H2" s="1">
-        <v>8</v>
+        <v>3000</v>
       </c>
       <c r="I2" s="1" t="s">
         <v>19</v>
@@ -676,300 +553,6 @@
       </c>
       <c r="L2" s="1" t="s">
         <v>21</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="H3" s="1">
-        <v>10500</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="H4" s="1">
-        <v>12000</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="L4" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="H5" s="1">
-        <v>22400</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="J5" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="K5" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="L5" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="H6" s="1">
-        <v>5600</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="J6" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="L6" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="H7" s="1">
-        <v>11200</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="J7" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="K7" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="L7" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="H8" s="1">
-        <v>5600</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="J8" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="K8" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="L8" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="H9" s="1">
-        <v>2600</v>
-      </c>
-      <c r="I9" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="J9" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="K9" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="L9" s="1" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="H10" s="1">
-        <v>5600</v>
-      </c>
-      <c r="I10" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="J10" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="K10" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="L10" s="1" t="s">
-        <v>62</v>
       </c>
     </row>
   </sheetData>

--- a/anthola_fullstack/backend/exports/bookings-latest.xlsx
+++ b/anthola_fullstack/backend/exports/bookings-latest.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="41">
   <si>
     <t>Booking ID</t>
   </si>
@@ -49,12 +49,75 @@
     <t>Created at</t>
   </si>
   <si>
+    <t>BKG-1785858443846-236</t>
+  </si>
+  <si>
+    <t>BUS</t>
+  </si>
+  <si>
+    <t>ayush</t>
+  </si>
+  <si>
+    <t>ktm -&gt; mnr</t>
+  </si>
+  <si>
+    <t>1234</t>
+  </si>
+  <si>
+    <t>2026-08-05</t>
+  </si>
+  <si>
+    <t>S02</t>
+  </si>
+  <si>
+    <t>NPR</t>
+  </si>
+  <si>
+    <t>VERIFIED</t>
+  </si>
+  <si>
+    <t>2026-08-04T15:47:23.855Z</t>
+  </si>
+  <si>
+    <t>BKG-1785856182145-120</t>
+  </si>
+  <si>
+    <t>2026-08-04</t>
+  </si>
+  <si>
+    <t>S09 | S10</t>
+  </si>
+  <si>
+    <t>PENDING_PAYMENT</t>
+  </si>
+  <si>
+    <t>PENDING</t>
+  </si>
+  <si>
+    <t>2026-08-04T15:09:42.147Z</t>
+  </si>
+  <si>
+    <t>BKG-1785855878390-596</t>
+  </si>
+  <si>
+    <t>S05 | S06</t>
+  </si>
+  <si>
+    <t>2026-08-04T15:04:38.393Z</t>
+  </si>
+  <si>
+    <t>BKG-1785855713851-286</t>
+  </si>
+  <si>
+    <t>S01 | S02 | S03 | S04</t>
+  </si>
+  <si>
+    <t>2026-08-04T15:01:53.857Z</t>
+  </si>
+  <si>
     <t>BKG-1785835183317-407</t>
   </si>
   <si>
-    <t>BUS</t>
-  </si>
-  <si>
     <t>kshitiz.thapa</t>
   </si>
   <si>
@@ -64,13 +127,7 @@
     <t>ktm-pok</t>
   </si>
   <si>
-    <t>2026-08-04</t>
-  </si>
-  <si>
     <t>S01 | S02</t>
-  </si>
-  <si>
-    <t>NPR</t>
   </si>
   <si>
     <t>PAYMENT_UPLOADED</t>
@@ -463,7 +520,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L6"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="22" style="1" customWidth="1"/>
@@ -540,7 +597,7 @@
         <v>18</v>
       </c>
       <c r="H2" s="1">
-        <v>3000</v>
+        <v>3398</v>
       </c>
       <c r="I2" s="1" t="s">
         <v>19</v>
@@ -553,6 +610,158 @@
       </c>
       <c r="L2" s="1" t="s">
         <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H3" s="1">
+        <v>6796</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H4" s="1">
+        <v>6796</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H5" s="1">
+        <v>13592</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="H6" s="1">
+        <v>3000</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>
